--- a/data/GPS/Metricas_GPS14.xlsx
+++ b/data/GPS/Metricas_GPS14.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30506"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79A374F-705D-4AB1-9A9D-7DD7E82E23A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t>Fecha</t>
   </si>
@@ -132,33 +141,31 @@
   </si>
   <si>
     <t xml:space="preserve">Juan_Manuel_Ruiz </t>
-  </si>
-  <si>
-    <t>Denfensa Lateral</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -169,38 +176,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -208,7 +220,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -398,26 +410,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="25.25"/>
-    <col customWidth="1" min="3" max="3" width="133.25"/>
+    <col min="2" max="2" width="25.21875" customWidth="1"/>
+    <col min="3" max="3" width="133.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -426,21 +441,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -487,39 +503,39 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B2" s="1">
-        <v>145.717</v>
+        <v>145.71700000000001</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1">
-        <v>6.272</v>
+        <v>6.2720000000000002</v>
       </c>
       <c r="F2" s="1">
-        <v>0.844</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="G2" s="1">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>0.033</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="I2" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="K2" s="1">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="L2" s="1">
         <v>4.57</v>
@@ -528,15 +544,15 @@
         <v>-5.39</v>
       </c>
       <c r="N2" s="1">
-        <v>31.021</v>
+        <v>31.021000000000001</v>
       </c>
       <c r="O2" s="1">
-        <v>1366.099</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>1366.0989999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B3" s="1">
         <v>147.233</v>
@@ -551,42 +567,42 @@
         <v>11.763</v>
       </c>
       <c r="F3" s="1">
-        <v>0.837</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="G3" s="1">
         <v>0.123</v>
       </c>
       <c r="H3" s="1">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="I3" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J3" s="1">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="K3" s="1">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="L3" s="1">
-        <v>4.483</v>
+        <v>4.4829999999999997</v>
       </c>
       <c r="M3" s="1">
-        <v>-5.475</v>
+        <v>-5.4749999999999996</v>
       </c>
       <c r="N3" s="1">
-        <v>30.175</v>
+        <v>30.175000000000001</v>
       </c>
       <c r="O3" s="1">
-        <v>2668.678</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>2668.6779999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B4" s="1">
-        <v>135.967</v>
+        <v>135.96700000000001</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>21</v>
@@ -598,42 +614,42 @@
         <v>10.436</v>
       </c>
       <c r="F4" s="1">
-        <v>0.579</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="G4" s="1">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="H4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="K4" s="1">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="L4" s="1">
         <v>5.21</v>
       </c>
       <c r="M4" s="1">
-        <v>-6.049</v>
+        <v>-6.0490000000000004</v>
       </c>
       <c r="N4" s="1">
-        <v>27.356</v>
+        <v>27.356000000000002</v>
       </c>
       <c r="O4" s="1">
-        <v>2079.137</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>2079.1370000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B5" s="1">
-        <v>143.867</v>
+        <v>143.86699999999999</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>23</v>
@@ -642,45 +658,45 @@
         <v>24</v>
       </c>
       <c r="E5" s="1">
-        <v>3.808</v>
+        <v>3.8079999999999998</v>
       </c>
       <c r="F5" s="1">
         <v>0.313</v>
       </c>
       <c r="G5" s="1">
-        <v>0.021</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="K5" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L5" s="1">
-        <v>4.805</v>
+        <v>4.8049999999999997</v>
       </c>
       <c r="M5" s="1">
-        <v>-7.058</v>
+        <v>-7.0579999999999998</v>
       </c>
       <c r="N5" s="1">
-        <v>26.932</v>
+        <v>26.931999999999999</v>
       </c>
       <c r="O5" s="1">
-        <v>817.864</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>817.86400000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B6" s="1">
-        <v>149.367</v>
+        <v>149.36699999999999</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>25</v>
@@ -689,45 +705,45 @@
         <v>26</v>
       </c>
       <c r="E6" s="1">
-        <v>4.042</v>
+        <v>4.0419999999999998</v>
       </c>
       <c r="F6" s="1">
-        <v>0.352</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="G6" s="1">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="H6" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="K6" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="L6" s="1">
-        <v>5.539</v>
+        <v>5.5389999999999997</v>
       </c>
       <c r="M6" s="1">
-        <v>-4.925</v>
+        <v>-4.9249999999999998</v>
       </c>
       <c r="N6" s="1">
-        <v>25.571</v>
+        <v>25.571000000000002</v>
       </c>
       <c r="O6" s="1">
-        <v>810.295</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>810.29499999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B7" s="1">
-        <v>145.033</v>
+        <v>145.03299999999999</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>27</v>
@@ -739,28 +755,28 @@
         <v>2.048</v>
       </c>
       <c r="F7" s="1">
-        <v>0.042</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="K7" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="L7" s="1">
-        <v>5.186</v>
+        <v>5.1859999999999999</v>
       </c>
       <c r="M7" s="1">
-        <v>-4.839</v>
+        <v>-4.8390000000000004</v>
       </c>
       <c r="N7" s="1">
         <v>23.087</v>
@@ -769,12 +785,12 @@
         <v>276.738</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B8" s="1">
-        <v>151.633</v>
+        <v>151.63300000000001</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -786,39 +802,39 @@
         <v>11.182</v>
       </c>
       <c r="F8" s="1">
-        <v>0.545</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="G8" s="1">
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="H8" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J8" s="1">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="K8" s="1">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="L8" s="1">
-        <v>5.583</v>
+        <v>5.5830000000000002</v>
       </c>
       <c r="M8" s="1">
-        <v>-6.268</v>
+        <v>-6.2679999999999998</v>
       </c>
       <c r="N8" s="1">
-        <v>27.925</v>
+        <v>27.925000000000001</v>
       </c>
       <c r="O8" s="1">
-        <v>2475.039</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>2475.0390000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B9" s="1">
         <v>121.3</v>
@@ -830,42 +846,42 @@
         <v>30</v>
       </c>
       <c r="E9" s="1">
-        <v>7.613</v>
+        <v>7.6130000000000004</v>
       </c>
       <c r="F9" s="1">
         <v>0.745</v>
       </c>
       <c r="G9" s="1">
-        <v>0.144</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="I9" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="J9" s="1">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="K9" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="L9" s="1">
-        <v>4.474</v>
+        <v>4.4740000000000002</v>
       </c>
       <c r="M9" s="1">
-        <v>-7.293</v>
+        <v>-7.2930000000000001</v>
       </c>
       <c r="N9" s="1">
-        <v>34.52</v>
+        <v>34.520000000000003</v>
       </c>
       <c r="O9" s="1">
-        <v>1222.631</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>1222.6310000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B10" s="1">
         <v>121.517</v>
@@ -880,39 +896,39 @@
         <v>8.327</v>
       </c>
       <c r="F10" s="1">
-        <v>0.743</v>
+        <v>0.74299999999999999</v>
       </c>
       <c r="G10" s="1">
         <v>0.121</v>
       </c>
       <c r="H10" s="1">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="I10" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="J10" s="1">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="K10" s="1">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="L10" s="1">
-        <v>5.023</v>
+        <v>5.0229999999999997</v>
       </c>
       <c r="M10" s="1">
-        <v>-6.183</v>
+        <v>-6.1829999999999998</v>
       </c>
       <c r="N10" s="1">
-        <v>30.708</v>
+        <v>30.707999999999998</v>
       </c>
       <c r="O10" s="1">
-        <v>1971.503</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1971.5029999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B11" s="1">
         <v>150.15</v>
@@ -927,42 +943,42 @@
         <v>13.352</v>
       </c>
       <c r="F11" s="1">
-        <v>1.455</v>
+        <v>1.4550000000000001</v>
       </c>
       <c r="G11" s="1">
-        <v>0.273</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="H11" s="1">
-        <v>0.054</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="I11" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="J11" s="1">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="K11" s="1">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="L11" s="1">
-        <v>5.714</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="M11" s="1">
-        <v>-6.833</v>
+        <v>-6.8330000000000002</v>
       </c>
       <c r="N11" s="1">
-        <v>31.626</v>
+        <v>31.626000000000001</v>
       </c>
       <c r="O11" s="1">
-        <v>2379.555</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>2379.5549999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B12" s="1">
-        <v>151.567</v>
+        <v>151.56700000000001</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
@@ -971,7 +987,7 @@
         <v>26</v>
       </c>
       <c r="E12" s="1">
-        <v>12.639</v>
+        <v>12.638999999999999</v>
       </c>
       <c r="F12" s="1">
         <v>1.107</v>
@@ -980,36 +996,36 @@
         <v>0.127</v>
       </c>
       <c r="H12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="J12" s="1">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="K12" s="1">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="L12" s="1">
-        <v>4.428</v>
+        <v>4.4279999999999999</v>
       </c>
       <c r="M12" s="1">
         <v>-6.633</v>
       </c>
       <c r="N12" s="1">
-        <v>28.094</v>
+        <v>28.094000000000001</v>
       </c>
       <c r="O12" s="1">
-        <v>3343.648</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>3343.6480000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B13" s="1">
-        <v>135.45</v>
+        <v>135.44999999999999</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>35</v>
@@ -1018,42 +1034,42 @@
         <v>26</v>
       </c>
       <c r="E13" s="1">
-        <v>9.966</v>
+        <v>9.9659999999999993</v>
       </c>
       <c r="F13" s="1">
-        <v>0.596</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="G13" s="1">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="H13" s="1">
-        <v>0.012</v>
+        <v>1.2E-2</v>
       </c>
       <c r="I13" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="K13" s="1">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="L13" s="1">
-        <v>4.619</v>
+        <v>4.6189999999999998</v>
       </c>
       <c r="M13" s="1">
-        <v>-6.522</v>
+        <v>-6.5220000000000002</v>
       </c>
       <c r="N13" s="1">
-        <v>29.923</v>
+        <v>29.922999999999998</v>
       </c>
       <c r="O13" s="1">
         <v>1852.434</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B14" s="1">
         <v>150.517</v>
@@ -1065,45 +1081,45 @@
         <v>30</v>
       </c>
       <c r="E14" s="1">
-        <v>6.203</v>
+        <v>6.2030000000000003</v>
       </c>
       <c r="F14" s="1">
-        <v>0.577</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="G14" s="1">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="H14" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="K14" s="1">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="L14" s="1">
-        <v>4.325</v>
+        <v>4.3250000000000002</v>
       </c>
       <c r="M14" s="1">
-        <v>-4.964</v>
+        <v>-4.9640000000000004</v>
       </c>
       <c r="N14" s="1">
-        <v>26.964</v>
+        <v>26.963999999999999</v>
       </c>
       <c r="O14" s="1">
-        <v>1202.294</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>1202.2940000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B15" s="1">
-        <v>108.067</v>
+        <v>108.06699999999999</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>37</v>
@@ -1112,28 +1128,28 @@
         <v>24</v>
       </c>
       <c r="E15" s="1">
-        <v>8.972</v>
+        <v>8.9719999999999995</v>
       </c>
       <c r="F15" s="1">
-        <v>0.912</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="G15" s="1">
-        <v>0.136</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="I15" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="J15" s="1">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="K15" s="1">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="L15" s="1">
-        <v>4.927</v>
+        <v>4.9269999999999996</v>
       </c>
       <c r="M15" s="1">
         <v>-5.931</v>
@@ -1145,9 +1161,9 @@
         <v>2214.252</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B16" s="1">
         <v>148.167</v>
@@ -1168,45 +1184,45 @@
         <v>0.129</v>
       </c>
       <c r="H16" s="1">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="I16" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="J16" s="1">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="K16" s="1">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="L16" s="1">
         <v>5.173</v>
       </c>
       <c r="M16" s="1">
-        <v>-5.701</v>
+        <v>-5.7009999999999996</v>
       </c>
       <c r="N16" s="1">
-        <v>29.333</v>
+        <v>29.332999999999998</v>
       </c>
       <c r="O16" s="1">
-        <v>3032.264</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>3032.2640000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="B17" s="1">
-        <v>147.45</v>
+        <v>147.44999999999999</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E17" s="1">
-        <v>5.461</v>
+        <v>5.4610000000000003</v>
       </c>
       <c r="F17" s="1">
         <v>0.47</v>
@@ -1215,16 +1231,16 @@
         <v>0.128</v>
       </c>
       <c r="H17" s="1">
-        <v>0.037</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="I17" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J17" s="1">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="K17" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="L17" s="1">
         <v>5.07</v>
@@ -1233,13 +1249,13 @@
         <v>-6.258</v>
       </c>
       <c r="N17" s="1">
-        <v>30.845</v>
+        <v>30.844999999999999</v>
       </c>
       <c r="O17" s="1">
         <v>1002.03</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>